--- a/employees.xlsx
+++ b/employees.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\c drive\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\c drive\Desktop\AttendanceApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A94BC80-A569-4A93-B41D-CE95366B4A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A99C04-E0DF-4F26-A748-920B07AE07EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D4E9C15E-F891-4000-9A20-B3956DD813A3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>ABHIMANYU RAI</t>
   </si>
@@ -93,16 +93,84 @@
   </si>
   <si>
     <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>LaN@#101</t>
+  </si>
+  <si>
+    <t>LaN@#102</t>
+  </si>
+  <si>
+    <t>LaN@#103</t>
+  </si>
+  <si>
+    <t>LaN@#104</t>
+  </si>
+  <si>
+    <t>LaN@#105</t>
+  </si>
+  <si>
+    <t>LaN@#106</t>
+  </si>
+  <si>
+    <t>LaN@#107</t>
+  </si>
+  <si>
+    <t>LaN@#108</t>
+  </si>
+  <si>
+    <t>LaN@#109</t>
+  </si>
+  <si>
+    <t>LaN@#110</t>
+  </si>
+  <si>
+    <t>LaN@#111</t>
+  </si>
+  <si>
+    <t>LaN@#112</t>
+  </si>
+  <si>
+    <t>LaN@#113</t>
+  </si>
+  <si>
+    <t>LaN@#114</t>
+  </si>
+  <si>
+    <t>LaN@#115</t>
+  </si>
+  <si>
+    <t>LaN@#116</t>
+  </si>
+  <si>
+    <t>LaN@#117</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -125,13 +193,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -464,100 +535,177 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05086051-BA7A-454D-AA79-C799FE33130F}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
+      <c r="B18" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{BA587C59-520F-40BD-B15C-6012382EDC98}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{9649D9A8-2B1F-44A6-B00D-FF3E6CDCC7D7}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{B4F35132-0584-4FF6-B784-942CB4024D4A}"/>
+    <hyperlink ref="B5" r:id="rId4" display="LaN@#101" xr:uid="{90486540-7AC9-4063-BFCC-7CED9CCA611A}"/>
+    <hyperlink ref="B8" r:id="rId5" display="LaN@#101" xr:uid="{909DDCC3-5600-4A27-9B1B-F5C186412833}"/>
+    <hyperlink ref="B11" r:id="rId6" display="LaN@#101" xr:uid="{4B3DEC95-6E98-48BE-ABE2-35106F376E98}"/>
+    <hyperlink ref="B14" r:id="rId7" display="LaN@#101" xr:uid="{27366B29-D43B-42CE-8419-E15680D0DAA8}"/>
+    <hyperlink ref="B17" r:id="rId8" display="LaN@#101" xr:uid="{4BE4B424-F432-45F5-A406-8CB0EDDFDA26}"/>
+    <hyperlink ref="B6" r:id="rId9" display="LaN@#102" xr:uid="{E48C4378-AD5A-411C-A2D9-E96F10463F63}"/>
+    <hyperlink ref="B9" r:id="rId10" display="LaN@#102" xr:uid="{46F68314-F168-47FB-BA71-18B69BE1D454}"/>
+    <hyperlink ref="B12" r:id="rId11" display="LaN@#102" xr:uid="{6678C5E4-DC60-4013-A72B-188166D9633C}"/>
+    <hyperlink ref="B15" r:id="rId12" display="LaN@#102" xr:uid="{BDD2FF6F-C4A0-4FEA-8D8C-A086DA4AC47E}"/>
+    <hyperlink ref="B18" r:id="rId13" display="LaN@#103" xr:uid="{5E6CED10-FC42-4A45-A754-58679C8BC196}"/>
+    <hyperlink ref="B7" r:id="rId14" display="LaN@#103" xr:uid="{6F600530-8B4B-4CF0-8A9F-3CAE38C0E25F}"/>
+    <hyperlink ref="B10" r:id="rId15" display="LaN@#103" xr:uid="{C42469E8-F28E-4FA3-9601-87753D49A2ED}"/>
+    <hyperlink ref="B13" r:id="rId16" display="LaN@#103" xr:uid="{4EFFDEE9-5574-497A-B4B4-55210D29DC04}"/>
+    <hyperlink ref="B16" r:id="rId17" display="LaN@#103" xr:uid="{5AE9A59F-001C-4B86-A647-B2EAE095AC21}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/employees.xlsx
+++ b/employees.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\c drive\Desktop\AttendanceApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A99C04-E0DF-4F26-A748-920B07AE07EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5DAEAB-63FB-42A7-9F2A-C86CFC427490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D4E9C15E-F891-4000-9A20-B3956DD813A3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>ABHIMANYU RAI</t>
   </si>
@@ -147,6 +147,12 @@
   </si>
   <si>
     <t>LaN@#117</t>
+  </si>
+  <si>
+    <t>Babli Kashyap</t>
+  </si>
+  <si>
+    <t>LaN@#118</t>
   </si>
 </sst>
 </file>
@@ -535,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05086051-BA7A-454D-AA79-C799FE33130F}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
@@ -683,6 +689,14 @@
       </c>
       <c r="B18" s="1" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -705,6 +719,7 @@
     <hyperlink ref="B10" r:id="rId15" display="LaN@#103" xr:uid="{C42469E8-F28E-4FA3-9601-87753D49A2ED}"/>
     <hyperlink ref="B13" r:id="rId16" display="LaN@#103" xr:uid="{4EFFDEE9-5574-497A-B4B4-55210D29DC04}"/>
     <hyperlink ref="B16" r:id="rId17" display="LaN@#103" xr:uid="{5AE9A59F-001C-4B86-A647-B2EAE095AC21}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{ED2C2520-33DA-48F4-B62E-E892F785ED98}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
